--- a/backend/excel-files/results_electrical_engineering_sem1.xlsx
+++ b/backend/excel-files/results_electrical_engineering_sem1.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E117"/>
+  <dimension ref="A1:E133"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -427,10 +427,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>UMaT/PG/0016/22</v>
+        <v>UMaT/PG/0001/22</v>
       </c>
       <c r="B2" t="str">
-        <v>Kobina Owusu</v>
+        <v>Yaa Nkrumah</v>
       </c>
       <c r="C2" t="str">
         <v>Engineering Economics</v>
@@ -439,15 +439,15 @@
         <v>3</v>
       </c>
       <c r="E2">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>UMaT/PG/0016/22</v>
+        <v>UMaT/PG/0001/22</v>
       </c>
       <c r="B3" t="str">
-        <v>Kobina Owusu</v>
+        <v>Yaa Nkrumah</v>
       </c>
       <c r="C3" t="str">
         <v>Modelling and Simulation</v>
@@ -456,15 +456,15 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>UMaT/PG/0016/22</v>
+        <v>UMaT/PG/0001/22</v>
       </c>
       <c r="B4" t="str">
-        <v>Kobina Owusu</v>
+        <v>Yaa Nkrumah</v>
       </c>
       <c r="C4" t="str">
         <v>Advanced Signal Processing</v>
@@ -473,15 +473,15 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>UMaT/PG/0016/22</v>
+        <v>UMaT/PG/0001/22</v>
       </c>
       <c r="B5" t="str">
-        <v>Kobina Owusu</v>
+        <v>Yaa Nkrumah</v>
       </c>
       <c r="C5" t="str">
         <v>Microprocessor Systems</v>
@@ -490,15 +490,15 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>UMaT/PG/0035/22</v>
+        <v>UMaT/PG/0017/22</v>
       </c>
       <c r="B6" t="str">
-        <v>Esi Boateng</v>
+        <v>Kwaku Opoku</v>
       </c>
       <c r="C6" t="str">
         <v>Engineering Economics</v>
@@ -507,15 +507,15 @@
         <v>3</v>
       </c>
       <c r="E6">
-        <v>62</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>UMaT/PG/0035/22</v>
+        <v>UMaT/PG/0017/22</v>
       </c>
       <c r="B7" t="str">
-        <v>Esi Boateng</v>
+        <v>Kwaku Opoku</v>
       </c>
       <c r="C7" t="str">
         <v>Modelling and Simulation</v>
@@ -524,15 +524,15 @@
         <v>3</v>
       </c>
       <c r="E7">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>UMaT/PG/0035/22</v>
+        <v>UMaT/PG/0017/22</v>
       </c>
       <c r="B8" t="str">
-        <v>Esi Boateng</v>
+        <v>Kwaku Opoku</v>
       </c>
       <c r="C8" t="str">
         <v>Advanced Signal Processing</v>
@@ -541,15 +541,15 @@
         <v>3</v>
       </c>
       <c r="E8">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>UMaT/PG/0035/22</v>
+        <v>UMaT/PG/0017/22</v>
       </c>
       <c r="B9" t="str">
-        <v>Esi Boateng</v>
+        <v>Kwaku Opoku</v>
       </c>
       <c r="C9" t="str">
         <v>Microprocessor Systems</v>
@@ -558,15 +558,15 @@
         <v>3</v>
       </c>
       <c r="E9">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>UMaT/PG/0047/22</v>
+        <v>UMaT/PG/0033/22</v>
       </c>
       <c r="B10" t="str">
-        <v>Panyin Addo</v>
+        <v>Kwadwo Mensah</v>
       </c>
       <c r="C10" t="str">
         <v>Engineering Economics</v>
@@ -575,15 +575,15 @@
         <v>3</v>
       </c>
       <c r="E10">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>UMaT/PG/0047/22</v>
+        <v>UMaT/PG/0033/22</v>
       </c>
       <c r="B11" t="str">
-        <v>Panyin Addo</v>
+        <v>Kwadwo Mensah</v>
       </c>
       <c r="C11" t="str">
         <v>Modelling and Simulation</v>
@@ -592,15 +592,15 @@
         <v>3</v>
       </c>
       <c r="E11">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>UMaT/PG/0047/22</v>
+        <v>UMaT/PG/0033/22</v>
       </c>
       <c r="B12" t="str">
-        <v>Panyin Addo</v>
+        <v>Kwadwo Mensah</v>
       </c>
       <c r="C12" t="str">
         <v>Advanced Signal Processing</v>
@@ -609,15 +609,15 @@
         <v>3</v>
       </c>
       <c r="E12">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>UMaT/PG/0047/22</v>
+        <v>UMaT/PG/0033/22</v>
       </c>
       <c r="B13" t="str">
-        <v>Panyin Addo</v>
+        <v>Kwadwo Mensah</v>
       </c>
       <c r="C13" t="str">
         <v>Microprocessor Systems</v>
@@ -626,15 +626,15 @@
         <v>3</v>
       </c>
       <c r="E13">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>UMaT/PG/0051/22</v>
+        <v>UMaT/PG/0058/22</v>
       </c>
       <c r="B14" t="str">
-        <v>Abena Nkrumah</v>
+        <v>Mensah Appiah</v>
       </c>
       <c r="C14" t="str">
         <v>Engineering Economics</v>
@@ -643,15 +643,15 @@
         <v>3</v>
       </c>
       <c r="E14">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>UMaT/PG/0051/22</v>
+        <v>UMaT/PG/0058/22</v>
       </c>
       <c r="B15" t="str">
-        <v>Abena Nkrumah</v>
+        <v>Mensah Appiah</v>
       </c>
       <c r="C15" t="str">
         <v>Modelling and Simulation</v>
@@ -660,15 +660,15 @@
         <v>3</v>
       </c>
       <c r="E15">
-        <v>51</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>UMaT/PG/0051/22</v>
+        <v>UMaT/PG/0058/22</v>
       </c>
       <c r="B16" t="str">
-        <v>Abena Nkrumah</v>
+        <v>Mensah Appiah</v>
       </c>
       <c r="C16" t="str">
         <v>Advanced Signal Processing</v>
@@ -677,15 +677,15 @@
         <v>3</v>
       </c>
       <c r="E16">
-        <v>91</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>UMaT/PG/0051/22</v>
+        <v>UMaT/PG/0058/22</v>
       </c>
       <c r="B17" t="str">
-        <v>Abena Nkrumah</v>
+        <v>Mensah Appiah</v>
       </c>
       <c r="C17" t="str">
         <v>Microprocessor Systems</v>
@@ -699,7 +699,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>UMaT/PG/0071/22</v>
+        <v>UMaT/PG/0062/22</v>
       </c>
       <c r="B18" t="str">
         <v>Akosua Wiredu</v>
@@ -711,12 +711,12 @@
         <v>3</v>
       </c>
       <c r="E18">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>UMaT/PG/0071/22</v>
+        <v>UMaT/PG/0062/22</v>
       </c>
       <c r="B19" t="str">
         <v>Akosua Wiredu</v>
@@ -728,12 +728,12 @@
         <v>3</v>
       </c>
       <c r="E19">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>UMaT/PG/0071/22</v>
+        <v>UMaT/PG/0062/22</v>
       </c>
       <c r="B20" t="str">
         <v>Akosua Wiredu</v>
@@ -750,7 +750,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>UMaT/PG/0071/22</v>
+        <v>UMaT/PG/0062/22</v>
       </c>
       <c r="B21" t="str">
         <v>Akosua Wiredu</v>
@@ -762,15 +762,15 @@
         <v>3</v>
       </c>
       <c r="E21">
-        <v>91</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>UMaT/PG/0074/22</v>
+        <v>UMaT/PG/0065/22</v>
       </c>
       <c r="B22" t="str">
-        <v>Kwaku Danquah</v>
+        <v>Adjoa Opoku</v>
       </c>
       <c r="C22" t="str">
         <v>Engineering Economics</v>
@@ -779,15 +779,15 @@
         <v>3</v>
       </c>
       <c r="E22">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>UMaT/PG/0074/22</v>
+        <v>UMaT/PG/0065/22</v>
       </c>
       <c r="B23" t="str">
-        <v>Kwaku Danquah</v>
+        <v>Adjoa Opoku</v>
       </c>
       <c r="C23" t="str">
         <v>Modelling and Simulation</v>
@@ -796,15 +796,15 @@
         <v>3</v>
       </c>
       <c r="E23">
-        <v>56</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>UMaT/PG/0074/22</v>
+        <v>UMaT/PG/0065/22</v>
       </c>
       <c r="B24" t="str">
-        <v>Kwaku Danquah</v>
+        <v>Adjoa Opoku</v>
       </c>
       <c r="C24" t="str">
         <v>Advanced Signal Processing</v>
@@ -813,15 +813,15 @@
         <v>3</v>
       </c>
       <c r="E24">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>UMaT/PG/0074/22</v>
+        <v>UMaT/PG/0065/22</v>
       </c>
       <c r="B25" t="str">
-        <v>Kwaku Danquah</v>
+        <v>Adjoa Opoku</v>
       </c>
       <c r="C25" t="str">
         <v>Microprocessor Systems</v>
@@ -830,15 +830,15 @@
         <v>3</v>
       </c>
       <c r="E25">
-        <v>89</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>UMaT/PG/0100/24</v>
+        <v>UMaT/PG/0066/22</v>
       </c>
       <c r="B26" t="str">
-        <v>Araba Darko</v>
+        <v>Mansa Boateng</v>
       </c>
       <c r="C26" t="str">
         <v>Engineering Economics</v>
@@ -847,15 +847,15 @@
         <v>3</v>
       </c>
       <c r="E26">
-        <v>58</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>UMaT/PG/0100/24</v>
+        <v>UMaT/PG/0066/22</v>
       </c>
       <c r="B27" t="str">
-        <v>Araba Darko</v>
+        <v>Mansa Boateng</v>
       </c>
       <c r="C27" t="str">
         <v>Modelling and Simulation</v>
@@ -864,15 +864,15 @@
         <v>3</v>
       </c>
       <c r="E27">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>UMaT/PG/0100/24</v>
+        <v>UMaT/PG/0066/22</v>
       </c>
       <c r="B28" t="str">
-        <v>Araba Darko</v>
+        <v>Mansa Boateng</v>
       </c>
       <c r="C28" t="str">
         <v>Advanced Signal Processing</v>
@@ -881,15 +881,15 @@
         <v>3</v>
       </c>
       <c r="E28">
-        <v>60</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>UMaT/PG/0100/24</v>
+        <v>UMaT/PG/0066/22</v>
       </c>
       <c r="B29" t="str">
-        <v>Araba Darko</v>
+        <v>Mansa Boateng</v>
       </c>
       <c r="C29" t="str">
         <v>Microprocessor Systems</v>
@@ -898,15 +898,15 @@
         <v>3</v>
       </c>
       <c r="E29">
-        <v>48</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>UMaT/PG/0103/24</v>
+        <v>UMaT/PG/0078/24</v>
       </c>
       <c r="B30" t="str">
-        <v>Kobina Gyasi</v>
+        <v>Mansa Sarpong</v>
       </c>
       <c r="C30" t="str">
         <v>Engineering Economics</v>
@@ -915,15 +915,15 @@
         <v>3</v>
       </c>
       <c r="E30">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>UMaT/PG/0103/24</v>
+        <v>UMaT/PG/0078/24</v>
       </c>
       <c r="B31" t="str">
-        <v>Kobina Gyasi</v>
+        <v>Mansa Sarpong</v>
       </c>
       <c r="C31" t="str">
         <v>Modelling and Simulation</v>
@@ -932,15 +932,15 @@
         <v>3</v>
       </c>
       <c r="E31">
-        <v>73</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>UMaT/PG/0103/24</v>
+        <v>UMaT/PG/0078/24</v>
       </c>
       <c r="B32" t="str">
-        <v>Kobina Gyasi</v>
+        <v>Mansa Sarpong</v>
       </c>
       <c r="C32" t="str">
         <v>Advanced Signal Processing</v>
@@ -949,15 +949,15 @@
         <v>3</v>
       </c>
       <c r="E32">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>UMaT/PG/0103/24</v>
+        <v>UMaT/PG/0078/24</v>
       </c>
       <c r="B33" t="str">
-        <v>Kobina Gyasi</v>
+        <v>Mansa Sarpong</v>
       </c>
       <c r="C33" t="str">
         <v>Microprocessor Systems</v>
@@ -966,15 +966,15 @@
         <v>3</v>
       </c>
       <c r="E33">
-        <v>40</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>UMaT/PG/0107/24</v>
+        <v>UMaT/PG/0081/24</v>
       </c>
       <c r="B34" t="str">
-        <v>Kwadwo Sarpong</v>
+        <v>Kwabena Nkrumah</v>
       </c>
       <c r="C34" t="str">
         <v>Engineering Economics</v>
@@ -983,15 +983,15 @@
         <v>3</v>
       </c>
       <c r="E34">
-        <v>40</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>UMaT/PG/0107/24</v>
+        <v>UMaT/PG/0081/24</v>
       </c>
       <c r="B35" t="str">
-        <v>Kwadwo Sarpong</v>
+        <v>Kwabena Nkrumah</v>
       </c>
       <c r="C35" t="str">
         <v>Modelling and Simulation</v>
@@ -1000,15 +1000,15 @@
         <v>3</v>
       </c>
       <c r="E35">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>UMaT/PG/0107/24</v>
+        <v>UMaT/PG/0081/24</v>
       </c>
       <c r="B36" t="str">
-        <v>Kwadwo Sarpong</v>
+        <v>Kwabena Nkrumah</v>
       </c>
       <c r="C36" t="str">
         <v>Advanced Signal Processing</v>
@@ -1017,15 +1017,15 @@
         <v>3</v>
       </c>
       <c r="E36">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>UMaT/PG/0107/24</v>
+        <v>UMaT/PG/0081/24</v>
       </c>
       <c r="B37" t="str">
-        <v>Kwadwo Sarpong</v>
+        <v>Kwabena Nkrumah</v>
       </c>
       <c r="C37" t="str">
         <v>Microprocessor Systems</v>
@@ -1034,15 +1034,15 @@
         <v>3</v>
       </c>
       <c r="E37">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>UMaT/PG/0114/24</v>
+        <v>UMaT/PG/0082/24</v>
       </c>
       <c r="B38" t="str">
-        <v>Kwadwo Boakye</v>
+        <v>Ebo Addo</v>
       </c>
       <c r="C38" t="str">
         <v>Engineering Economics</v>
@@ -1051,15 +1051,15 @@
         <v>3</v>
       </c>
       <c r="E38">
-        <v>65</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>UMaT/PG/0114/24</v>
+        <v>UMaT/PG/0082/24</v>
       </c>
       <c r="B39" t="str">
-        <v>Kwadwo Boakye</v>
+        <v>Ebo Addo</v>
       </c>
       <c r="C39" t="str">
         <v>Modelling and Simulation</v>
@@ -1068,15 +1068,15 @@
         <v>3</v>
       </c>
       <c r="E39">
-        <v>66</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>UMaT/PG/0114/24</v>
+        <v>UMaT/PG/0082/24</v>
       </c>
       <c r="B40" t="str">
-        <v>Kwadwo Boakye</v>
+        <v>Ebo Addo</v>
       </c>
       <c r="C40" t="str">
         <v>Advanced Signal Processing</v>
@@ -1085,15 +1085,15 @@
         <v>3</v>
       </c>
       <c r="E40">
-        <v>67</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>UMaT/PG/0114/24</v>
+        <v>UMaT/PG/0082/24</v>
       </c>
       <c r="B41" t="str">
-        <v>Kwadwo Boakye</v>
+        <v>Ebo Addo</v>
       </c>
       <c r="C41" t="str">
         <v>Microprocessor Systems</v>
@@ -1102,15 +1102,15 @@
         <v>3</v>
       </c>
       <c r="E41">
-        <v>56</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>UMaT/PG/0129/24</v>
+        <v>UMaT/PG/0107/24</v>
       </c>
       <c r="B42" t="str">
-        <v>Akua Owusu</v>
+        <v>Efua Appiah</v>
       </c>
       <c r="C42" t="str">
         <v>Engineering Economics</v>
@@ -1119,15 +1119,15 @@
         <v>3</v>
       </c>
       <c r="E42">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>UMaT/PG/0129/24</v>
+        <v>UMaT/PG/0107/24</v>
       </c>
       <c r="B43" t="str">
-        <v>Akua Owusu</v>
+        <v>Efua Appiah</v>
       </c>
       <c r="C43" t="str">
         <v>Modelling and Simulation</v>
@@ -1136,15 +1136,15 @@
         <v>3</v>
       </c>
       <c r="E43">
-        <v>61</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>UMaT/PG/0129/24</v>
+        <v>UMaT/PG/0107/24</v>
       </c>
       <c r="B44" t="str">
-        <v>Akua Owusu</v>
+        <v>Efua Appiah</v>
       </c>
       <c r="C44" t="str">
         <v>Advanced Signal Processing</v>
@@ -1153,15 +1153,15 @@
         <v>3</v>
       </c>
       <c r="E44">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>UMaT/PG/0129/24</v>
+        <v>UMaT/PG/0107/24</v>
       </c>
       <c r="B45" t="str">
-        <v>Akua Owusu</v>
+        <v>Efua Appiah</v>
       </c>
       <c r="C45" t="str">
         <v>Microprocessor Systems</v>
@@ -1170,15 +1170,15 @@
         <v>3</v>
       </c>
       <c r="E45">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>UMaT/PG/0133/24</v>
+        <v>UMaT/PG/0112/24</v>
       </c>
       <c r="B46" t="str">
-        <v>Serwa Agyei</v>
+        <v>Kwesi Amoah</v>
       </c>
       <c r="C46" t="str">
         <v>Engineering Economics</v>
@@ -1187,15 +1187,15 @@
         <v>3</v>
       </c>
       <c r="E46">
-        <v>72</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>UMaT/PG/0133/24</v>
+        <v>UMaT/PG/0112/24</v>
       </c>
       <c r="B47" t="str">
-        <v>Serwa Agyei</v>
+        <v>Kwesi Amoah</v>
       </c>
       <c r="C47" t="str">
         <v>Modelling and Simulation</v>
@@ -1204,15 +1204,15 @@
         <v>3</v>
       </c>
       <c r="E47">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>UMaT/PG/0133/24</v>
+        <v>UMaT/PG/0112/24</v>
       </c>
       <c r="B48" t="str">
-        <v>Serwa Agyei</v>
+        <v>Kwesi Amoah</v>
       </c>
       <c r="C48" t="str">
         <v>Advanced Signal Processing</v>
@@ -1221,15 +1221,15 @@
         <v>3</v>
       </c>
       <c r="E48">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>UMaT/PG/0133/24</v>
+        <v>UMaT/PG/0112/24</v>
       </c>
       <c r="B49" t="str">
-        <v>Serwa Agyei</v>
+        <v>Kwesi Amoah</v>
       </c>
       <c r="C49" t="str">
         <v>Microprocessor Systems</v>
@@ -1238,15 +1238,15 @@
         <v>3</v>
       </c>
       <c r="E49">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>UMaT/PG/0163/24</v>
+        <v>UMaT/PG/0114/24</v>
       </c>
       <c r="B50" t="str">
-        <v>Akua Yeboah</v>
+        <v>Kofi Amankwah</v>
       </c>
       <c r="C50" t="str">
         <v>Engineering Economics</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>UMaT/PG/0163/24</v>
+        <v>UMaT/PG/0114/24</v>
       </c>
       <c r="B51" t="str">
-        <v>Akua Yeboah</v>
+        <v>Kofi Amankwah</v>
       </c>
       <c r="C51" t="str">
         <v>Modelling and Simulation</v>
@@ -1272,15 +1272,15 @@
         <v>3</v>
       </c>
       <c r="E51">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>UMaT/PG/0163/24</v>
+        <v>UMaT/PG/0114/24</v>
       </c>
       <c r="B52" t="str">
-        <v>Akua Yeboah</v>
+        <v>Kofi Amankwah</v>
       </c>
       <c r="C52" t="str">
         <v>Advanced Signal Processing</v>
@@ -1289,15 +1289,15 @@
         <v>3</v>
       </c>
       <c r="E52">
-        <v>83</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>UMaT/PG/0163/24</v>
+        <v>UMaT/PG/0114/24</v>
       </c>
       <c r="B53" t="str">
-        <v>Akua Yeboah</v>
+        <v>Kofi Amankwah</v>
       </c>
       <c r="C53" t="str">
         <v>Microprocessor Systems</v>
@@ -1306,15 +1306,15 @@
         <v>3</v>
       </c>
       <c r="E53">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>UMaT/PG/0175/24</v>
+        <v>UMaT/PG/0129/24</v>
       </c>
       <c r="B54" t="str">
-        <v>Ato Wiredu</v>
+        <v>Kwaku Agyemang</v>
       </c>
       <c r="C54" t="str">
         <v>Engineering Economics</v>
@@ -1323,15 +1323,15 @@
         <v>3</v>
       </c>
       <c r="E54">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>UMaT/PG/0175/24</v>
+        <v>UMaT/PG/0129/24</v>
       </c>
       <c r="B55" t="str">
-        <v>Ato Wiredu</v>
+        <v>Kwaku Agyemang</v>
       </c>
       <c r="C55" t="str">
         <v>Modelling and Simulation</v>
@@ -1340,15 +1340,15 @@
         <v>3</v>
       </c>
       <c r="E55">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>UMaT/PG/0175/24</v>
+        <v>UMaT/PG/0129/24</v>
       </c>
       <c r="B56" t="str">
-        <v>Ato Wiredu</v>
+        <v>Kwaku Agyemang</v>
       </c>
       <c r="C56" t="str">
         <v>Advanced Signal Processing</v>
@@ -1357,15 +1357,15 @@
         <v>3</v>
       </c>
       <c r="E56">
-        <v>63</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>UMaT/PG/0175/24</v>
+        <v>UMaT/PG/0129/24</v>
       </c>
       <c r="B57" t="str">
-        <v>Ato Wiredu</v>
+        <v>Kwaku Agyemang</v>
       </c>
       <c r="C57" t="str">
         <v>Microprocessor Systems</v>
@@ -1374,15 +1374,15 @@
         <v>3</v>
       </c>
       <c r="E57">
-        <v>78</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>UMaT/PG/0182/24</v>
+        <v>UMaT/PG/0137/24</v>
       </c>
       <c r="B58" t="str">
-        <v>Yaw Quaye</v>
+        <v>Esi Mensah</v>
       </c>
       <c r="C58" t="str">
         <v>Engineering Economics</v>
@@ -1391,15 +1391,15 @@
         <v>3</v>
       </c>
       <c r="E58">
-        <v>72</v>
+        <v>57</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>UMaT/PG/0182/24</v>
+        <v>UMaT/PG/0137/24</v>
       </c>
       <c r="B59" t="str">
-        <v>Yaw Quaye</v>
+        <v>Esi Mensah</v>
       </c>
       <c r="C59" t="str">
         <v>Modelling and Simulation</v>
@@ -1408,15 +1408,15 @@
         <v>3</v>
       </c>
       <c r="E59">
-        <v>52</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>UMaT/PG/0182/24</v>
+        <v>UMaT/PG/0137/24</v>
       </c>
       <c r="B60" t="str">
-        <v>Yaw Quaye</v>
+        <v>Esi Mensah</v>
       </c>
       <c r="C60" t="str">
         <v>Advanced Signal Processing</v>
@@ -1425,15 +1425,15 @@
         <v>3</v>
       </c>
       <c r="E60">
-        <v>40</v>
+        <v>74</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>UMaT/PG/0182/24</v>
+        <v>UMaT/PG/0137/24</v>
       </c>
       <c r="B61" t="str">
-        <v>Yaw Quaye</v>
+        <v>Esi Mensah</v>
       </c>
       <c r="C61" t="str">
         <v>Microprocessor Systems</v>
@@ -1442,15 +1442,15 @@
         <v>3</v>
       </c>
       <c r="E61">
-        <v>61</v>
+        <v>42</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>UMaT/PG/0187/24</v>
+        <v>UMaT/PG/0149/24</v>
       </c>
       <c r="B62" t="str">
-        <v>Afia Boakye</v>
+        <v>Ebo Quaye</v>
       </c>
       <c r="C62" t="str">
         <v>Engineering Economics</v>
@@ -1459,15 +1459,15 @@
         <v>3</v>
       </c>
       <c r="E62">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>UMaT/PG/0187/24</v>
+        <v>UMaT/PG/0149/24</v>
       </c>
       <c r="B63" t="str">
-        <v>Afia Boakye</v>
+        <v>Ebo Quaye</v>
       </c>
       <c r="C63" t="str">
         <v>Modelling and Simulation</v>
@@ -1476,15 +1476,15 @@
         <v>3</v>
       </c>
       <c r="E63">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>UMaT/PG/0187/24</v>
+        <v>UMaT/PG/0149/24</v>
       </c>
       <c r="B64" t="str">
-        <v>Afia Boakye</v>
+        <v>Ebo Quaye</v>
       </c>
       <c r="C64" t="str">
         <v>Advanced Signal Processing</v>
@@ -1493,15 +1493,15 @@
         <v>3</v>
       </c>
       <c r="E64">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>UMaT/PG/0187/24</v>
+        <v>UMaT/PG/0149/24</v>
       </c>
       <c r="B65" t="str">
-        <v>Afia Boakye</v>
+        <v>Ebo Quaye</v>
       </c>
       <c r="C65" t="str">
         <v>Microprocessor Systems</v>
@@ -1510,15 +1510,15 @@
         <v>3</v>
       </c>
       <c r="E65">
-        <v>53</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>UMaT/PG/0192/24</v>
+        <v>UMaT/PG/0150/24</v>
       </c>
       <c r="B66" t="str">
-        <v>Araba Boakye</v>
+        <v>Kodwo Mensah</v>
       </c>
       <c r="C66" t="str">
         <v>Engineering Economics</v>
@@ -1527,15 +1527,15 @@
         <v>3</v>
       </c>
       <c r="E66">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>UMaT/PG/0192/24</v>
+        <v>UMaT/PG/0150/24</v>
       </c>
       <c r="B67" t="str">
-        <v>Araba Boakye</v>
+        <v>Kodwo Mensah</v>
       </c>
       <c r="C67" t="str">
         <v>Modelling and Simulation</v>
@@ -1544,15 +1544,15 @@
         <v>3</v>
       </c>
       <c r="E67">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>UMaT/PG/0192/24</v>
+        <v>UMaT/PG/0150/24</v>
       </c>
       <c r="B68" t="str">
-        <v>Araba Boakye</v>
+        <v>Kodwo Mensah</v>
       </c>
       <c r="C68" t="str">
         <v>Advanced Signal Processing</v>
@@ -1561,15 +1561,15 @@
         <v>3</v>
       </c>
       <c r="E68">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>UMaT/PG/0192/24</v>
+        <v>UMaT/PG/0150/24</v>
       </c>
       <c r="B69" t="str">
-        <v>Araba Boakye</v>
+        <v>Kodwo Mensah</v>
       </c>
       <c r="C69" t="str">
         <v>Microprocessor Systems</v>
@@ -1578,15 +1578,15 @@
         <v>3</v>
       </c>
       <c r="E69">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>UMaT/PG/0199/24</v>
+        <v>UMaT/PG/0171/24</v>
       </c>
       <c r="B70" t="str">
-        <v>Kwabena Akuffo</v>
+        <v>Kwadwo Akuffo</v>
       </c>
       <c r="C70" t="str">
         <v>Engineering Economics</v>
@@ -1595,15 +1595,15 @@
         <v>3</v>
       </c>
       <c r="E70">
-        <v>45</v>
+        <v>68</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>UMaT/PG/0199/24</v>
+        <v>UMaT/PG/0171/24</v>
       </c>
       <c r="B71" t="str">
-        <v>Kwabena Akuffo</v>
+        <v>Kwadwo Akuffo</v>
       </c>
       <c r="C71" t="str">
         <v>Modelling and Simulation</v>
@@ -1612,15 +1612,15 @@
         <v>3</v>
       </c>
       <c r="E71">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>UMaT/PG/0199/24</v>
+        <v>UMaT/PG/0171/24</v>
       </c>
       <c r="B72" t="str">
-        <v>Kwabena Akuffo</v>
+        <v>Kwadwo Akuffo</v>
       </c>
       <c r="C72" t="str">
         <v>Advanced Signal Processing</v>
@@ -1629,15 +1629,15 @@
         <v>3</v>
       </c>
       <c r="E72">
-        <v>63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>UMaT/PG/0199/24</v>
+        <v>UMaT/PG/0171/24</v>
       </c>
       <c r="B73" t="str">
-        <v>Kwabena Akuffo</v>
+        <v>Kwadwo Akuffo</v>
       </c>
       <c r="C73" t="str">
         <v>Microprocessor Systems</v>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>UMaT/PG/0204/24</v>
+        <v>UMaT/PG/0180/24</v>
       </c>
       <c r="B74" t="str">
-        <v>Kodwo Appiah</v>
+        <v>Akosua Boateng</v>
       </c>
       <c r="C74" t="str">
         <v>Engineering Economics</v>
@@ -1663,15 +1663,15 @@
         <v>3</v>
       </c>
       <c r="E74">
-        <v>53</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>UMaT/PG/0204/24</v>
+        <v>UMaT/PG/0180/24</v>
       </c>
       <c r="B75" t="str">
-        <v>Kodwo Appiah</v>
+        <v>Akosua Boateng</v>
       </c>
       <c r="C75" t="str">
         <v>Modelling and Simulation</v>
@@ -1680,15 +1680,15 @@
         <v>3</v>
       </c>
       <c r="E75">
-        <v>54</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>UMaT/PG/0204/24</v>
+        <v>UMaT/PG/0180/24</v>
       </c>
       <c r="B76" t="str">
-        <v>Kodwo Appiah</v>
+        <v>Akosua Boateng</v>
       </c>
       <c r="C76" t="str">
         <v>Advanced Signal Processing</v>
@@ -1697,15 +1697,15 @@
         <v>3</v>
       </c>
       <c r="E76">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>UMaT/PG/0204/24</v>
+        <v>UMaT/PG/0180/24</v>
       </c>
       <c r="B77" t="str">
-        <v>Kodwo Appiah</v>
+        <v>Akosua Boateng</v>
       </c>
       <c r="C77" t="str">
         <v>Microprocessor Systems</v>
@@ -1714,15 +1714,15 @@
         <v>3</v>
       </c>
       <c r="E77">
-        <v>43</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>UMaT/PG/0207/24</v>
+        <v>UMaT/PG/0188/24</v>
       </c>
       <c r="B78" t="str">
-        <v>Kwabena Boateng</v>
+        <v>Kwadwo Asante</v>
       </c>
       <c r="C78" t="str">
         <v>Engineering Economics</v>
@@ -1731,15 +1731,15 @@
         <v>3</v>
       </c>
       <c r="E78">
-        <v>93</v>
+        <v>60</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>UMaT/PG/0207/24</v>
+        <v>UMaT/PG/0188/24</v>
       </c>
       <c r="B79" t="str">
-        <v>Kwabena Boateng</v>
+        <v>Kwadwo Asante</v>
       </c>
       <c r="C79" t="str">
         <v>Modelling and Simulation</v>
@@ -1748,15 +1748,15 @@
         <v>3</v>
       </c>
       <c r="E79">
-        <v>60</v>
+        <v>79</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>UMaT/PG/0207/24</v>
+        <v>UMaT/PG/0188/24</v>
       </c>
       <c r="B80" t="str">
-        <v>Kwabena Boateng</v>
+        <v>Kwadwo Asante</v>
       </c>
       <c r="C80" t="str">
         <v>Advanced Signal Processing</v>
@@ -1765,15 +1765,15 @@
         <v>3</v>
       </c>
       <c r="E80">
-        <v>42</v>
+        <v>66</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>UMaT/PG/0207/24</v>
+        <v>UMaT/PG/0188/24</v>
       </c>
       <c r="B81" t="str">
-        <v>Kwabena Boateng</v>
+        <v>Kwadwo Asante</v>
       </c>
       <c r="C81" t="str">
         <v>Microprocessor Systems</v>
@@ -1782,15 +1782,15 @@
         <v>3</v>
       </c>
       <c r="E81">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>UMaT/PG/0213/24</v>
+        <v>UMaT/PG/0196/24</v>
       </c>
       <c r="B82" t="str">
-        <v>Kobina Asante</v>
+        <v>Serwa Ofori</v>
       </c>
       <c r="C82" t="str">
         <v>Engineering Economics</v>
@@ -1799,15 +1799,15 @@
         <v>3</v>
       </c>
       <c r="E82">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>UMaT/PG/0213/24</v>
+        <v>UMaT/PG/0196/24</v>
       </c>
       <c r="B83" t="str">
-        <v>Kobina Asante</v>
+        <v>Serwa Ofori</v>
       </c>
       <c r="C83" t="str">
         <v>Modelling and Simulation</v>
@@ -1816,15 +1816,15 @@
         <v>3</v>
       </c>
       <c r="E83">
-        <v>42</v>
+        <v>59</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>UMaT/PG/0213/24</v>
+        <v>UMaT/PG/0196/24</v>
       </c>
       <c r="B84" t="str">
-        <v>Kobina Asante</v>
+        <v>Serwa Ofori</v>
       </c>
       <c r="C84" t="str">
         <v>Advanced Signal Processing</v>
@@ -1833,15 +1833,15 @@
         <v>3</v>
       </c>
       <c r="E84">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>UMaT/PG/0213/24</v>
+        <v>UMaT/PG/0196/24</v>
       </c>
       <c r="B85" t="str">
-        <v>Kobina Asante</v>
+        <v>Serwa Ofori</v>
       </c>
       <c r="C85" t="str">
         <v>Microprocessor Systems</v>
@@ -1850,15 +1850,15 @@
         <v>3</v>
       </c>
       <c r="E85">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>UMaT/PG/0215/24</v>
+        <v>UMaT/PG/0212/24</v>
       </c>
       <c r="B86" t="str">
-        <v>Yaa Afriyie</v>
+        <v>Mensah Acheampong</v>
       </c>
       <c r="C86" t="str">
         <v>Engineering Economics</v>
@@ -1867,15 +1867,15 @@
         <v>3</v>
       </c>
       <c r="E86">
-        <v>77</v>
+        <v>55</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>UMaT/PG/0215/24</v>
+        <v>UMaT/PG/0212/24</v>
       </c>
       <c r="B87" t="str">
-        <v>Yaa Afriyie</v>
+        <v>Mensah Acheampong</v>
       </c>
       <c r="C87" t="str">
         <v>Modelling and Simulation</v>
@@ -1884,15 +1884,15 @@
         <v>3</v>
       </c>
       <c r="E87">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>UMaT/PG/0215/24</v>
+        <v>UMaT/PG/0212/24</v>
       </c>
       <c r="B88" t="str">
-        <v>Yaa Afriyie</v>
+        <v>Mensah Acheampong</v>
       </c>
       <c r="C88" t="str">
         <v>Advanced Signal Processing</v>
@@ -1901,15 +1901,15 @@
         <v>3</v>
       </c>
       <c r="E88">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>UMaT/PG/0215/24</v>
+        <v>UMaT/PG/0212/24</v>
       </c>
       <c r="B89" t="str">
-        <v>Yaa Afriyie</v>
+        <v>Mensah Acheampong</v>
       </c>
       <c r="C89" t="str">
         <v>Microprocessor Systems</v>
@@ -1918,15 +1918,15 @@
         <v>3</v>
       </c>
       <c r="E89">
-        <v>78</v>
+        <v>54</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>UMaT/PG/0220/24</v>
+        <v>UMaT/PG/0218/24</v>
       </c>
       <c r="B90" t="str">
-        <v>Kwabena Asante</v>
+        <v>Afi Amoah</v>
       </c>
       <c r="C90" t="str">
         <v>Engineering Economics</v>
@@ -1935,15 +1935,15 @@
         <v>3</v>
       </c>
       <c r="E90">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>UMaT/PG/0220/24</v>
+        <v>UMaT/PG/0218/24</v>
       </c>
       <c r="B91" t="str">
-        <v>Kwabena Asante</v>
+        <v>Afi Amoah</v>
       </c>
       <c r="C91" t="str">
         <v>Modelling and Simulation</v>
@@ -1952,15 +1952,15 @@
         <v>3</v>
       </c>
       <c r="E91">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>UMaT/PG/0220/24</v>
+        <v>UMaT/PG/0218/24</v>
       </c>
       <c r="B92" t="str">
-        <v>Kwabena Asante</v>
+        <v>Afi Amoah</v>
       </c>
       <c r="C92" t="str">
         <v>Advanced Signal Processing</v>
@@ -1969,15 +1969,15 @@
         <v>3</v>
       </c>
       <c r="E92">
-        <v>86</v>
+        <v>60</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>UMaT/PG/0220/24</v>
+        <v>UMaT/PG/0218/24</v>
       </c>
       <c r="B93" t="str">
-        <v>Kwabena Asante</v>
+        <v>Afi Amoah</v>
       </c>
       <c r="C93" t="str">
         <v>Microprocessor Systems</v>
@@ -1986,15 +1986,15 @@
         <v>3</v>
       </c>
       <c r="E93">
-        <v>42</v>
+        <v>77</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>UMaT/PG/0244/24</v>
+        <v>UMaT/PG/0249/24</v>
       </c>
       <c r="B94" t="str">
-        <v>Kobina Ofori</v>
+        <v>Abena Boakye</v>
       </c>
       <c r="C94" t="str">
         <v>Engineering Economics</v>
@@ -2003,15 +2003,15 @@
         <v>3</v>
       </c>
       <c r="E94">
-        <v>78</v>
+        <v>51</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>UMaT/PG/0244/24</v>
+        <v>UMaT/PG/0249/24</v>
       </c>
       <c r="B95" t="str">
-        <v>Kobina Ofori</v>
+        <v>Abena Boakye</v>
       </c>
       <c r="C95" t="str">
         <v>Modelling and Simulation</v>
@@ -2020,15 +2020,15 @@
         <v>3</v>
       </c>
       <c r="E95">
-        <v>69</v>
+        <v>97</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>UMaT/PG/0244/24</v>
+        <v>UMaT/PG/0249/24</v>
       </c>
       <c r="B96" t="str">
-        <v>Kobina Ofori</v>
+        <v>Abena Boakye</v>
       </c>
       <c r="C96" t="str">
         <v>Advanced Signal Processing</v>
@@ -2037,15 +2037,15 @@
         <v>3</v>
       </c>
       <c r="E96">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>UMaT/PG/0244/24</v>
+        <v>UMaT/PG/0249/24</v>
       </c>
       <c r="B97" t="str">
-        <v>Kobina Ofori</v>
+        <v>Abena Boakye</v>
       </c>
       <c r="C97" t="str">
         <v>Microprocessor Systems</v>
@@ -2054,15 +2054,15 @@
         <v>3</v>
       </c>
       <c r="E97">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>UMaT/PG/0255/24</v>
+        <v>UMaT/PG/0262/24</v>
       </c>
       <c r="B98" t="str">
-        <v>Ato Amankwah</v>
+        <v>Ebo Agyemang</v>
       </c>
       <c r="C98" t="str">
         <v>Engineering Economics</v>
@@ -2071,15 +2071,15 @@
         <v>3</v>
       </c>
       <c r="E98">
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>UMaT/PG/0255/24</v>
+        <v>UMaT/PG/0262/24</v>
       </c>
       <c r="B99" t="str">
-        <v>Ato Amankwah</v>
+        <v>Ebo Agyemang</v>
       </c>
       <c r="C99" t="str">
         <v>Modelling and Simulation</v>
@@ -2088,15 +2088,15 @@
         <v>3</v>
       </c>
       <c r="E99">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>UMaT/PG/0255/24</v>
+        <v>UMaT/PG/0262/24</v>
       </c>
       <c r="B100" t="str">
-        <v>Ato Amankwah</v>
+        <v>Ebo Agyemang</v>
       </c>
       <c r="C100" t="str">
         <v>Advanced Signal Processing</v>
@@ -2105,15 +2105,15 @@
         <v>3</v>
       </c>
       <c r="E100">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>UMaT/PG/0255/24</v>
+        <v>UMaT/PG/0262/24</v>
       </c>
       <c r="B101" t="str">
-        <v>Ato Amankwah</v>
+        <v>Ebo Agyemang</v>
       </c>
       <c r="C101" t="str">
         <v>Microprocessor Systems</v>
@@ -2122,15 +2122,15 @@
         <v>3</v>
       </c>
       <c r="E101">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>UMaT/PG/0261/24</v>
+        <v>UMaT/PG/0266/24</v>
       </c>
       <c r="B102" t="str">
-        <v>Efua Danquah</v>
+        <v>Panyin Amankwah</v>
       </c>
       <c r="C102" t="str">
         <v>Engineering Economics</v>
@@ -2139,15 +2139,15 @@
         <v>3</v>
       </c>
       <c r="E102">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>UMaT/PG/0261/24</v>
+        <v>UMaT/PG/0266/24</v>
       </c>
       <c r="B103" t="str">
-        <v>Efua Danquah</v>
+        <v>Panyin Amankwah</v>
       </c>
       <c r="C103" t="str">
         <v>Modelling and Simulation</v>
@@ -2156,15 +2156,15 @@
         <v>3</v>
       </c>
       <c r="E103">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>UMaT/PG/0261/24</v>
+        <v>UMaT/PG/0266/24</v>
       </c>
       <c r="B104" t="str">
-        <v>Efua Danquah</v>
+        <v>Panyin Amankwah</v>
       </c>
       <c r="C104" t="str">
         <v>Advanced Signal Processing</v>
@@ -2173,15 +2173,15 @@
         <v>3</v>
       </c>
       <c r="E104">
-        <v>98</v>
+        <v>56</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>UMaT/PG/0261/24</v>
+        <v>UMaT/PG/0266/24</v>
       </c>
       <c r="B105" t="str">
-        <v>Efua Danquah</v>
+        <v>Panyin Amankwah</v>
       </c>
       <c r="C105" t="str">
         <v>Microprocessor Systems</v>
@@ -2190,15 +2190,15 @@
         <v>3</v>
       </c>
       <c r="E105">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>UMaT/PG/0263/24</v>
+        <v>UMaT/PG/0274/24</v>
       </c>
       <c r="B106" t="str">
-        <v>Ama Frimpong</v>
+        <v>Adjoa Amankwah</v>
       </c>
       <c r="C106" t="str">
         <v>Engineering Economics</v>
@@ -2207,15 +2207,15 @@
         <v>3</v>
       </c>
       <c r="E106">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>UMaT/PG/0263/24</v>
+        <v>UMaT/PG/0274/24</v>
       </c>
       <c r="B107" t="str">
-        <v>Ama Frimpong</v>
+        <v>Adjoa Amankwah</v>
       </c>
       <c r="C107" t="str">
         <v>Modelling and Simulation</v>
@@ -2224,15 +2224,15 @@
         <v>3</v>
       </c>
       <c r="E107">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>UMaT/PG/0263/24</v>
+        <v>UMaT/PG/0274/24</v>
       </c>
       <c r="B108" t="str">
-        <v>Ama Frimpong</v>
+        <v>Adjoa Amankwah</v>
       </c>
       <c r="C108" t="str">
         <v>Advanced Signal Processing</v>
@@ -2241,15 +2241,15 @@
         <v>3</v>
       </c>
       <c r="E108">
-        <v>79</v>
+        <v>65</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>UMaT/PG/0263/24</v>
+        <v>UMaT/PG/0274/24</v>
       </c>
       <c r="B109" t="str">
-        <v>Ama Frimpong</v>
+        <v>Adjoa Amankwah</v>
       </c>
       <c r="C109" t="str">
         <v>Microprocessor Systems</v>
@@ -2258,15 +2258,15 @@
         <v>3</v>
       </c>
       <c r="E109">
-        <v>49</v>
+        <v>60</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>UMaT/PG/0273/24</v>
+        <v>UMaT/PG/0279/24</v>
       </c>
       <c r="B110" t="str">
-        <v>Yaw Afriyie</v>
+        <v>Mansa Owusu</v>
       </c>
       <c r="C110" t="str">
         <v>Engineering Economics</v>
@@ -2275,15 +2275,15 @@
         <v>3</v>
       </c>
       <c r="E110">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>UMaT/PG/0273/24</v>
+        <v>UMaT/PG/0279/24</v>
       </c>
       <c r="B111" t="str">
-        <v>Yaw Afriyie</v>
+        <v>Mansa Owusu</v>
       </c>
       <c r="C111" t="str">
         <v>Modelling and Simulation</v>
@@ -2292,15 +2292,15 @@
         <v>3</v>
       </c>
       <c r="E111">
-        <v>65</v>
+        <v>79</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>UMaT/PG/0273/24</v>
+        <v>UMaT/PG/0279/24</v>
       </c>
       <c r="B112" t="str">
-        <v>Yaw Afriyie</v>
+        <v>Mansa Owusu</v>
       </c>
       <c r="C112" t="str">
         <v>Advanced Signal Processing</v>
@@ -2309,15 +2309,15 @@
         <v>3</v>
       </c>
       <c r="E112">
-        <v>41</v>
+        <v>67</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>UMaT/PG/0273/24</v>
+        <v>UMaT/PG/0279/24</v>
       </c>
       <c r="B113" t="str">
-        <v>Yaw Afriyie</v>
+        <v>Mansa Owusu</v>
       </c>
       <c r="C113" t="str">
         <v>Microprocessor Systems</v>
@@ -2326,15 +2326,15 @@
         <v>3</v>
       </c>
       <c r="E113">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>UMaT/PG/0292/24</v>
+        <v>UMaT/PG/0282/24</v>
       </c>
       <c r="B114" t="str">
-        <v>Kakra Asante</v>
+        <v>Efua Wiredu</v>
       </c>
       <c r="C114" t="str">
         <v>Engineering Economics</v>
@@ -2343,15 +2343,15 @@
         <v>3</v>
       </c>
       <c r="E114">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>UMaT/PG/0292/24</v>
+        <v>UMaT/PG/0282/24</v>
       </c>
       <c r="B115" t="str">
-        <v>Kakra Asante</v>
+        <v>Efua Wiredu</v>
       </c>
       <c r="C115" t="str">
         <v>Modelling and Simulation</v>
@@ -2360,15 +2360,15 @@
         <v>3</v>
       </c>
       <c r="E115">
-        <v>67</v>
+        <v>43</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>UMaT/PG/0292/24</v>
+        <v>UMaT/PG/0282/24</v>
       </c>
       <c r="B116" t="str">
-        <v>Kakra Asante</v>
+        <v>Efua Wiredu</v>
       </c>
       <c r="C116" t="str">
         <v>Advanced Signal Processing</v>
@@ -2377,15 +2377,15 @@
         <v>3</v>
       </c>
       <c r="E116">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>UMaT/PG/0292/24</v>
+        <v>UMaT/PG/0282/24</v>
       </c>
       <c r="B117" t="str">
-        <v>Kakra Asante</v>
+        <v>Efua Wiredu</v>
       </c>
       <c r="C117" t="str">
         <v>Microprocessor Systems</v>
@@ -2394,12 +2394,284 @@
         <v>3</v>
       </c>
       <c r="E117">
-        <v>79</v>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>UMaT/PG/0284/24</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Araba Osei</v>
+      </c>
+      <c r="C118" t="str">
+        <v>Engineering Economics</v>
+      </c>
+      <c r="D118">
+        <v>3</v>
+      </c>
+      <c r="E118">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>UMaT/PG/0284/24</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Araba Osei</v>
+      </c>
+      <c r="C119" t="str">
+        <v>Modelling and Simulation</v>
+      </c>
+      <c r="D119">
+        <v>3</v>
+      </c>
+      <c r="E119">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>UMaT/PG/0284/24</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Araba Osei</v>
+      </c>
+      <c r="C120" t="str">
+        <v>Advanced Signal Processing</v>
+      </c>
+      <c r="D120">
+        <v>3</v>
+      </c>
+      <c r="E120">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>UMaT/PG/0284/24</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Araba Osei</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Microprocessor Systems</v>
+      </c>
+      <c r="D121">
+        <v>3</v>
+      </c>
+      <c r="E121">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>UMaT/PG/0287/24</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Kwesi Darko</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Engineering Economics</v>
+      </c>
+      <c r="D122">
+        <v>3</v>
+      </c>
+      <c r="E122">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>UMaT/PG/0287/24</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Kwesi Darko</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Modelling and Simulation</v>
+      </c>
+      <c r="D123">
+        <v>3</v>
+      </c>
+      <c r="E123">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>UMaT/PG/0287/24</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Kwesi Darko</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Advanced Signal Processing</v>
+      </c>
+      <c r="D124">
+        <v>3</v>
+      </c>
+      <c r="E124">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>UMaT/PG/0287/24</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Kwesi Darko</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Microprocessor Systems</v>
+      </c>
+      <c r="D125">
+        <v>3</v>
+      </c>
+      <c r="E125">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>UMaT/PG/0299/24</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Adwoa Danquah</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Engineering Economics</v>
+      </c>
+      <c r="D126">
+        <v>3</v>
+      </c>
+      <c r="E126">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>UMaT/PG/0299/24</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Adwoa Danquah</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Modelling and Simulation</v>
+      </c>
+      <c r="D127">
+        <v>3</v>
+      </c>
+      <c r="E127">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>UMaT/PG/0299/24</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Adwoa Danquah</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Advanced Signal Processing</v>
+      </c>
+      <c r="D128">
+        <v>3</v>
+      </c>
+      <c r="E128">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>UMaT/PG/0299/24</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Adwoa Danquah</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Microprocessor Systems</v>
+      </c>
+      <c r="D129">
+        <v>3</v>
+      </c>
+      <c r="E129">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>UMaT/PG/0300/24</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Akosua Agyemang</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Engineering Economics</v>
+      </c>
+      <c r="D130">
+        <v>3</v>
+      </c>
+      <c r="E130">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>UMaT/PG/0300/24</v>
+      </c>
+      <c r="B131" t="str">
+        <v>Akosua Agyemang</v>
+      </c>
+      <c r="C131" t="str">
+        <v>Modelling and Simulation</v>
+      </c>
+      <c r="D131">
+        <v>3</v>
+      </c>
+      <c r="E131">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>UMaT/PG/0300/24</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Akosua Agyemang</v>
+      </c>
+      <c r="C132" t="str">
+        <v>Advanced Signal Processing</v>
+      </c>
+      <c r="D132">
+        <v>3</v>
+      </c>
+      <c r="E132">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>UMaT/PG/0300/24</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Akosua Agyemang</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Microprocessor Systems</v>
+      </c>
+      <c r="D133">
+        <v>3</v>
+      </c>
+      <c r="E133">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E117"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E133"/>
   </ignoredErrors>
 </worksheet>
 </file>